--- a/crates/unluminous-sheet/tests/fixtures/pages/pages-times.xlsx
+++ b/crates/unluminous-sheet/tests/fixtures/pages/pages-times.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\jason\dev\unluminous\.claude\worktrees\agent-afa636fef9f2b0676\crates\unluminous-sheet\tests\fixtures\pages\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1BC888D9-E050-49FE-89D0-113A1C0487C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{220E57A5-84C6-4A7F-816F-CBE47AE5058D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1875" yWindow="6660" windowWidth="43200" windowHeight="23445" activeTab="6" xr2:uid="{8F02C392-95E0-411C-A682-0760B1113EAA}"/>
+    <workbookView xWindow="1875" yWindow="6660" windowWidth="43200" windowHeight="23445" activeTab="6" xr2:uid="{13CE3CF3-0146-4171-B19B-2A0CDFAEE2A5}"/>
   </bookViews>
   <sheets>
     <sheet name="letter-p" sheetId="1" r:id="rId1"/>
@@ -412,7 +412,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A056EA86-9045-4274-BDD9-F2F64BF2B916}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F5FB3FC-9617-4FED-96C7-AC5157FE23D5}">
   <dimension ref="A1:AN130"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -16283,7 +16283,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33B11DB4-64A2-4D5B-B722-DA0D6FE972E8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{016A095A-68A3-42C4-B376-BBE3987CB16F}">
   <dimension ref="A1:AN130"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -32154,7 +32154,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D771BBA7-5024-473B-8C7B-72B202A2736C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15894673-07C5-454C-91EB-E6B82329CE41}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -48028,7 +48028,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D410E4CA-0FEC-4F94-BDDE-107785A70861}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F9B6A97-F1B3-4044-AFE3-E36F9B9D25A0}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -63902,7 +63902,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96DB88A3-EE00-4837-8C2F-136FB4A1E082}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6657B38-1970-4D22-AD67-0738BA67C35F}">
   <dimension ref="A1:AN130"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -79773,7 +79773,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABA005F8-84B3-4119-AE93-543A0B25D58B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8445377D-BC0D-4BAF-9D85-7293F0C69584}">
   <dimension ref="A1:AN130"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -95644,7 +95644,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23D63D95-05A9-4FCB-9976-9B9C73992A68}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{093B0152-0F50-46D2-AE98-27630BB420E3}">
   <dimension ref="A1:AN130"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
